--- a/data/trans_camb/IP19C08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,2; -1,99</t>
+          <t>-15,37; -1,71</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,36; -1,93</t>
+          <t>-16,29; -1,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,74; -1,95</t>
+          <t>-16,84; -1,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 4,09</t>
+          <t>-13,35; 3,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,81; -3,2</t>
+          <t>-17,02; -3,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,5; 5,66</t>
+          <t>-13,34; 5,31</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-10,83; -0,82</t>
+          <t>-11,29; -0,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,68; -3,78</t>
+          <t>-12,97; -3,31</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,93; -0,18</t>
+          <t>-10,78; 0,3</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 220,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 263,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-95,0; 21,59</t>
+          <t>-94,06; 19,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 53,7</t>
+          <t>-100,0; 92,11</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 3,33</t>
+          <t>-3,65; 3,31</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 2,68</t>
+          <t>-3,72; 2,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,78; -0,16</t>
+          <t>-5,89; -0,26</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 1,49</t>
+          <t>-4,45; 1,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 1,02</t>
+          <t>-4,52; 1,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 2,13</t>
+          <t>-5,24; 2,03</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 1,7</t>
+          <t>-3,16; 1,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 1,15</t>
+          <t>-3,35; 1,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; -0,0</t>
+          <t>-4,71; -0,16</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-51,65; 97,37</t>
+          <t>-52,96; 91,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-56,38; 74,52</t>
+          <t>-55,36; 84,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,54; 4,27</t>
+          <t>-83,84; 5,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-67,07; 42,27</t>
+          <t>-68,0; 41,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,7; 40,99</t>
+          <t>-69,81; 35,9</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-85,18; 90,95</t>
+          <t>-83,75; 79,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,89; 42,85</t>
+          <t>-49,03; 42,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 30,87</t>
+          <t>-52,53; 29,61</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-77,63; 4,65</t>
+          <t>-75,86; 14,1</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 2,7</t>
+          <t>-8,68; 3,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,18; -0,27</t>
+          <t>-11,05; -0,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 0,2</t>
+          <t>-11,0; 0,72</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,77; 6,15</t>
+          <t>-2,71; 6,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 2,43</t>
+          <t>-3,99; 2,48</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 7,16</t>
+          <t>-1,39; 7,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,11</t>
+          <t>-4,55; 3,09</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,19; 0,54</t>
+          <t>-6,26; 0,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 2,89</t>
+          <t>-3,94; 2,99</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,64; 101,55</t>
+          <t>-86,33; 118,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 31,32</t>
+          <t>-100,0; 14,74</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-91,24; 33,53</t>
+          <t>-90,69; 72,24</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-64,89; —</t>
+          <t>-60,0; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 124,91</t>
+          <t>-68,96; 158,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,75; 38,23</t>
+          <t>-89,73; 46,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 126,25</t>
+          <t>-61,75; 144,54</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 1,29</t>
+          <t>-4,28; 1,06</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,65; 0,75</t>
+          <t>-4,53; 0,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,23; -1,4</t>
+          <t>-6,07; -1,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 1,32</t>
+          <t>-3,75; 1,27</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 0,21</t>
+          <t>-4,47; 0,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,58</t>
+          <t>-4,01; 1,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 0,52</t>
+          <t>-3,16; 0,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; -0,23</t>
+          <t>-3,82; -0,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; -0,34</t>
+          <t>-4,17; -0,36</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,01; 31,32</t>
+          <t>-59,58; 26,06</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 19,33</t>
+          <t>-62,9; 22,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,87; -28,99</t>
+          <t>-81,98; -27,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,29; 41,08</t>
+          <t>-58,44; 38,3</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,3; 10,55</t>
+          <t>-72,14; 9,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 49,33</t>
+          <t>-65,86; 62,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-48,09; 13,32</t>
+          <t>-50,89; 11,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,72; -4,41</t>
+          <t>-60,35; -5,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,0; -5,12</t>
+          <t>-67,38; -7,5</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,37; -1,71</t>
+          <t>-14,88; -1,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -1,96</t>
+          <t>-15,65; -1,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,84; -1,75</t>
+          <t>-15,86; -1,73</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,35; 3,11</t>
+          <t>-13,81; 3,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-17,02; -3,05</t>
+          <t>-18,25; -3,15</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,34; 5,31</t>
+          <t>-12,86; 6,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -0,73</t>
+          <t>-11,13; -0,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,97; -3,31</t>
+          <t>-12,9; -3,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,78; 0,3</t>
+          <t>-10,88; -0,13</t>
         </is>
       </c>
     </row>
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 253,18</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 323,78</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 7,51</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-94,06; 19,55</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 92,11</t>
+          <t>-100,0; 85,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,65; 3,31</t>
+          <t>-3,47; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 2,76</t>
+          <t>-3,47; 2,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; -0,26</t>
+          <t>-6,01; -0,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 1,43</t>
+          <t>-4,84; 1,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 1,1</t>
+          <t>-4,83; 1,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 2,03</t>
+          <t>-5,38; 2,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 1,59</t>
+          <t>-3,13; 1,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 1,05</t>
+          <t>-3,34; 1,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; -0,16</t>
+          <t>-4,84; 0,1</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-52,96; 91,33</t>
+          <t>-49,54; 101,69</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-55,36; 84,76</t>
+          <t>-53,88; 86,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,84; 5,2</t>
+          <t>-83,28; 8,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,0; 41,25</t>
+          <t>-68,69; 36,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,81; 35,9</t>
+          <t>-69,93; 37,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-83,75; 79,76</t>
+          <t>-84,43; 99,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,03; 42,81</t>
+          <t>-49,62; 41,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-52,53; 29,61</t>
+          <t>-53,3; 24,41</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-75,86; 14,1</t>
+          <t>-76,4; 11,38</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 3,0</t>
+          <t>-8,98; 2,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,05; -0,24</t>
+          <t>-11,95; -0,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 0,72</t>
+          <t>-10,17; 0,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 6,34</t>
+          <t>-2,07; 6,12</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,48</t>
+          <t>-4,66; 2,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 7,37</t>
+          <t>-1,42; 7,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,09</t>
+          <t>-4,15; 2,94</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 0,3</t>
+          <t>-6,32; 0,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 2,99</t>
+          <t>-3,92; 2,95</t>
         </is>
       </c>
     </row>
@@ -1215,17 +1215,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-86,33; 118,21</t>
+          <t>-85,59; 111,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 14,74</t>
+          <t>-100,0; 30,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-90,69; 72,24</t>
+          <t>-92,3; 19,26</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-60,0; —</t>
+          <t>-56,24; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,96; 158,38</t>
+          <t>-69,14; 121,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-89,73; 46,6</t>
+          <t>-90,34; 26,89</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-61,75; 144,54</t>
+          <t>-60,86; 127,83</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 1,06</t>
+          <t>-4,36; 0,95</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 0,87</t>
+          <t>-4,54; 0,79</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,07; -1,31</t>
+          <t>-5,87; -1,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,27</t>
+          <t>-3,61; 1,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,47; 0,12</t>
+          <t>-4,63; 0,02</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 1,87</t>
+          <t>-3,99; 1,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,16; 0,43</t>
+          <t>-3,17; 0,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,82; -0,34</t>
+          <t>-3,81; -0,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,36</t>
+          <t>-4,23; -0,51</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,58; 26,06</t>
+          <t>-60,84; 24,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,9; 22,04</t>
+          <t>-62,76; 18,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,98; -27,66</t>
+          <t>-81,15; -26,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,44; 38,3</t>
+          <t>-58,58; 46,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 9,23</t>
+          <t>-73,75; 2,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-65,86; 62,66</t>
+          <t>-66,02; 53,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,89; 11,28</t>
+          <t>-50,27; 13,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,35; -5,23</t>
+          <t>-60,15; -3,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-67,38; -7,5</t>
+          <t>-68,31; -6,83</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C08-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP19C08-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,34 +624,34 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,72</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-8,18</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,12</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-6,51</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-6,51</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>-6,51</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,72</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-8,18</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-3,73</t>
-        </is>
-      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
           <t>-5,2</t>
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-5,25</t>
+          <t>-5,37</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-14,88; -1,72</t>
+          <t>-12,91; 4,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-15,65; -1,73</t>
+          <t>-18,81; -3,2</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -1,73</t>
+          <t>-13,71; 4,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,81; 3,96</t>
+          <t>-15,2; -1,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -3,15</t>
+          <t>-16,36; -1,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,86; 6,2</t>
+          <t>-15,74; -1,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,13; -0,91</t>
+          <t>-10,83; -0,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,9; -3,94</t>
+          <t>-12,68; -3,78</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,13</t>
+          <t>-11,08; -0,46</t>
         </is>
       </c>
     </row>
@@ -730,34 +730,34 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-45,42%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-50,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-45,42%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-45,58%</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
           <t>-71,12%</t>
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-71,88%</t>
+          <t>-73,51%</t>
         </is>
       </c>
     </row>
@@ -783,37 +783,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 220,68</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 233,49</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 253,18</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 323,78</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,51</t>
+          <t>-95,0; 21,59</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 85,67</t>
+          <t>-100,0; 50,97</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-1,41</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,83</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-2,34</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,01</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,42</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-2,86</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,41</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,83</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>-2,88</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-2,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 3,58</t>
+          <t>-4,53; 1,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 2,76</t>
+          <t>-4,77; 1,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -0,05</t>
+          <t>-5,38; 2,44</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,15</t>
+          <t>-3,48; 3,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 1,16</t>
+          <t>-3,97; 2,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,29</t>
+          <t>-5,8; -0,21</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 1,63</t>
+          <t>-3,09; 1,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 1,0</t>
+          <t>-3,28; 1,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 0,1</t>
+          <t>-4,79; 0,1</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-27,49%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-35,7%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-45,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-0,22%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-8,13%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-55,11%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-27,49%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-35,7%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-47,5%</t>
+          <t>-55,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-50,95%</t>
+          <t>-50,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 101,69</t>
+          <t>-67,07; 42,27</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,88; 86,72</t>
+          <t>-70,7; 40,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-83,28; 8,14</t>
+          <t>-85,06; 121,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-68,69; 36,63</t>
+          <t>-51,65; 97,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-69,93; 37,65</t>
+          <t>-56,38; 74,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-84,43; 99,1</t>
+          <t>-85,23; 2,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,62; 41,01</t>
+          <t>-47,89; 42,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-53,3; 24,41</t>
+          <t>-51,57; 30,87</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-76,4; 11,38</t>
+          <t>-77,54; 8,47</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>1,68</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,78</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-4,74</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-4,2</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,68</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>-4,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,5</t>
+          <t>-0,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 2,62</t>
+          <t>-2,77; 6,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -0,49</t>
+          <t>-4,52; 2,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 0,05</t>
+          <t>-1,12; 6,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 6,12</t>
+          <t>-9,08; 2,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 2,45</t>
+          <t>-11,18; -0,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 7,19</t>
+          <t>-10,11; -0,02</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 2,94</t>
+          <t>-4,12; 3,11</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 0,06</t>
+          <t>-6,19; 0,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 2,95</t>
+          <t>-4,55; 2,47</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>90,32%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-12,74%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>149,4%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-39,81%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-70,17%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-62,14%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>90,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-12,74%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>158,01%</t>
+          <t>-64,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-11,46%</t>
+          <t>-16,62%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-85,59; 111,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,79</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-92,3; 19,26</t>
+          <t>-67,92; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,64; 101,55</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 31,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-56,24; —</t>
+          <t>-91,64; 33,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-69,14; 121,72</t>
+          <t>-66,02; 124,91</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-90,34; 26,89</t>
+          <t>-90,75; 38,23</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,86; 127,83</t>
+          <t>-68,09; 113,94</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,19</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,46</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-1,89</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-3,5</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,19</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,45</t>
+          <t>-3,53</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-2,41</t>
+          <t>-2,45</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 0,95</t>
+          <t>-3,66; 1,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,79</t>
+          <t>-4,45; 0,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,87; -1,18</t>
+          <t>-4,01; 1,75</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 1,4</t>
+          <t>-4,22; 1,29</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 0,02</t>
+          <t>-4,65; 0,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,69</t>
+          <t>-6,29; -1,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,17; 0,57</t>
+          <t>-2,95; 0,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,81; -0,23</t>
+          <t>-3,69; -0,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,51</t>
+          <t>-3,99; -0,33</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-22,0%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-45,24%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-30,27%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-26,21%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-33,18%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-61,23%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-22,0%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-45,24%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,05%</t>
+          <t>-61,88%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-45,7%</t>
+          <t>-46,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-60,84; 24,26</t>
+          <t>-58,29; 41,08</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-62,76; 18,43</t>
+          <t>-72,3; 10,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-81,15; -26,09</t>
+          <t>-65,87; 53,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 46,11</t>
+          <t>-58,01; 31,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,75; 2,91</t>
+          <t>-63,25; 19,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-66,02; 53,05</t>
+          <t>-82,04; -29,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,27; 13,74</t>
+          <t>-48,09; 13,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-60,15; -3,77</t>
+          <t>-59,72; -4,41</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-68,31; -6,83</t>
+          <t>-65,62; -5,19</t>
         </is>
       </c>
     </row>
